--- a/dados/JOAO CRUZ CORONEL - 14497.xlsx
+++ b/dados/JOAO CRUZ CORONEL - 14497.xlsx
@@ -16,13 +16,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="76">
   <si>
-    <t>6º ao 9º EFAF</t>
+    <t>3ª EM</t>
   </si>
   <si>
     <t>1ª/2ª EM</t>
   </si>
   <si>
-    <t>3ª EM</t>
+    <t>6º ao 9º EFAF</t>
+  </si>
+  <si>
+    <t>Turma</t>
   </si>
   <si>
     <t>Total de Matrículas</t>
@@ -31,28 +34,49 @@
     <t>Alunos que fizeram a avaliação</t>
   </si>
   <si>
+    <t>Acertos em Língua Portuguesa (Questões 1, 2, 3, 4, 5)</t>
+  </si>
+  <si>
+    <t>Acertos em Matemática (Questões 6, 7, 8, 9, 10)</t>
+  </si>
+  <si>
+    <t>Acertos em Física (Questões 11, 12, 13, 14)</t>
+  </si>
+  <si>
+    <t>Acertos em História (Questões 15, 16, 17, 18)</t>
+  </si>
+  <si>
+    <t>Acertos em Língua Inglesa (Questões 19, 20, 21, 22)</t>
+  </si>
+  <si>
+    <t>Total de Acertos</t>
+  </si>
+  <si>
+    <t>3ª SERIE D INTEGRAL 7H T2 ANUAL - 40945194</t>
+  </si>
+  <si>
+    <t>Alunos (Pres.)</t>
+  </si>
+  <si>
+    <t>Total Matric.</t>
+  </si>
+  <si>
+    <t>Part. (%)</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Ciências</t>
+  </si>
+  <si>
+    <t>Filosofia</t>
+  </si>
+  <si>
     <t>Acertos em Língua Portuguesa (Questões 1, 2, 3, 4)</t>
   </si>
   <si>
     <t>Acertos em Matemática (Questões 5, 6, 7, 8)</t>
-  </si>
-  <si>
-    <t>Acertos em Língua Inglesa (Questões 9, 10, 11)</t>
-  </si>
-  <si>
-    <t>Acertos em Ciências (Questões 12, 13, 14)</t>
-  </si>
-  <si>
-    <t>Acertos em História (Questões 15, 16, 17)</t>
-  </si>
-  <si>
-    <t>Acertos em Geografia (Questões 18, 19, 20)</t>
-  </si>
-  <si>
-    <t>Turma</t>
-  </si>
-  <si>
-    <t>Total de Acertos</t>
   </si>
   <si>
     <t>Acertos em Física (Questões 9, 10)</t>
@@ -67,61 +91,22 @@
     <t>Acertos em História (Questões 15, 16)</t>
   </si>
   <si>
-    <t>6° ANO A INTEGRAL 7H T1 ANUAL - 40975446</t>
+    <t>Sociologia</t>
   </si>
   <si>
     <t>Acertos em Geografia (Questões 17, 18)</t>
   </si>
   <si>
+    <t>Física</t>
+  </si>
+  <si>
     <t>Acertos em Filosofia/Sociologia (Questões 19, 20)</t>
   </si>
   <si>
-    <t>Acertos em Língua Inglesa (Questões 21, 22)</t>
+    <t>Geografia</t>
   </si>
   <si>
-    <t>Alunos (Pres.)</t>
-  </si>
-  <si>
-    <t>Total Matric.</t>
-  </si>
-  <si>
-    <t>1ª SERIE A INTEGRAL 7H T2 ANUAL - 40967637</t>
-  </si>
-  <si>
-    <t>Part. (%)</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>Acertos em Língua Portuguesa (Questões 1, 2, 3, 4, 5)</t>
-  </si>
-  <si>
-    <t>Ciências</t>
-  </si>
-  <si>
-    <t>Acertos em Matemática (Questões 6, 7, 8, 9, 10)</t>
-  </si>
-  <si>
-    <t>Filosofia</t>
-  </si>
-  <si>
-    <t>Acertos em Física (Questões 11, 12, 13, 14)</t>
-  </si>
-  <si>
-    <t>Sociologia</t>
-  </si>
-  <si>
-    <t>Acertos em História (Questões 15, 16, 17, 18)</t>
-  </si>
-  <si>
-    <t>Física</t>
-  </si>
-  <si>
-    <t>Acertos em Língua Inglesa (Questões 19, 20, 21, 22)</t>
-  </si>
-  <si>
-    <t>Geografia</t>
+    <t>Acertos em Língua Inglesa (Questões 21, 22)</t>
   </si>
   <si>
     <t>História</t>
@@ -130,46 +115,73 @@
     <t>Língua Inglesa</t>
   </si>
   <si>
-    <t>3ª SERIE D INTEGRAL 7H T2 ANUAL - 40945194</t>
+    <t>Língua Portuguesa</t>
   </si>
   <si>
-    <t>Língua Portuguesa</t>
+    <t>1ª SERIE A INTEGRAL 7H T2 ANUAL - 40967637</t>
   </si>
   <si>
     <t>Matemática</t>
   </si>
   <si>
+    <t>Acertos em Língua Inglesa (Questões 9, 10, 11)</t>
+  </si>
+  <si>
     <t>Química</t>
+  </si>
+  <si>
+    <t>Acertos em Ciências (Questões 12, 13, 14)</t>
   </si>
   <si>
     <t>Média Geral</t>
   </si>
   <si>
+    <t>Acertos em História (Questões 15, 16, 17)</t>
+  </si>
+  <si>
+    <t>Acertos em Geografia (Questões 18, 19, 20)</t>
+  </si>
+  <si>
+    <t>6° ANO A INTEGRAL 7H T1 ANUAL - 40975446</t>
+  </si>
+  <si>
     <t>MÉDIA GLOBAL DA ESCOLA</t>
+  </si>
+  <si>
+    <t>3ª SERIE E NOITE ANUAL - 40945197</t>
   </si>
   <si>
     <t>6° ANO B INTEGRAL 7H T1 ANUAL - 40975447</t>
   </si>
   <si>
-    <t>1ª SERIE B INTEGRAL 7H T2 ANUAL - 40967638</t>
-  </si>
-  <si>
-    <t>3ª SERIE E NOITE ANUAL - 40945197</t>
+    <t>3ª SERIE F NOITE ANUAL - 40945196</t>
   </si>
   <si>
     <t>6° ANO C INTEGRAL 7H T1 ANUAL - 40975448</t>
   </si>
   <si>
-    <t>3ª SERIE F NOITE ANUAL - 40945196</t>
+    <t>3ª SERIE G NOITE ANUAL - 40945195</t>
+  </si>
+  <si>
+    <t>1ª SERIE B INTEGRAL 7H T2 ANUAL - 40967638</t>
   </si>
   <si>
     <t>6° ANO D INTEGRAL 7H T1 ANUAL - 40975449</t>
   </si>
   <si>
+    <t>3ª SERIE H NOITE ANUAL - 41373724</t>
+  </si>
+  <si>
+    <t>7° ANO A INTEGRAL 7H T1 ANUAL - 40907744</t>
+  </si>
+  <si>
+    <t>4050 - ADMINISTRAÇÃO - 3ª SERIE A INTEGRAL 7H T2 ANUAL - 40964108</t>
+  </si>
+  <si>
     <t>1ª SERIE C INTEGRAL 7H T2 ANUAL - 40967639</t>
   </si>
   <si>
-    <t>7° ANO A INTEGRAL 7H T1 ANUAL - 40907744</t>
+    <t>6082 - DESENVOLVIMENTO DE SISTEMAS - 3ª SERIE C INTEGRAL 7H T2 ANUAL - 40964109</t>
   </si>
   <si>
     <t>1ª SERIE D INTEGRAL 7H T2 ANUAL - 40967640</t>
@@ -178,31 +190,19 @@
     <t>7° ANO D INTEGRAL 7H T1 ANUAL - 40907751</t>
   </si>
   <si>
-    <t>3ª SERIE G NOITE ANUAL - 40945195</t>
-  </si>
-  <si>
     <t>7º ANO B INTEGRAL 7H T1 ANUAL - 40907747</t>
   </si>
   <si>
     <t>2ª SERIE D NOITE ANUAL - 41358801</t>
   </si>
   <si>
-    <t>3ª SERIE H NOITE ANUAL - 41373724</t>
-  </si>
-  <si>
     <t>7º ANO C INTEGRAL 7H T1 ANUAL - 40907746</t>
-  </si>
-  <si>
-    <t>4050 - ADMINISTRAÇÃO - 3ª SERIE A INTEGRAL 7H T2 ANUAL - 40964108</t>
-  </si>
-  <si>
-    <t>2ª SERIE E NOITE ANUAL - 41380193</t>
   </si>
   <si>
     <t>8º ANO A INTEGRAL 7H T1 ANUAL - 40907748</t>
   </si>
   <si>
-    <t>6082 - DESENVOLVIMENTO DE SISTEMAS - 3ª SERIE C INTEGRAL 7H T2 ANUAL - 40964109</t>
+    <t>2ª SERIE E NOITE ANUAL - 41380193</t>
   </si>
   <si>
     <t>8º ANO B INTEGRAL 7H T1 ANUAL - 40907752</t>
@@ -214,31 +214,31 @@
     <t>8º ANO C INTEGRAL 7H T1 ANUAL - 40907755</t>
   </si>
   <si>
+    <t>8º ANO D INTEGRAL 7H T1 ANUAL - 40907749</t>
+  </si>
+  <si>
     <t>2ª SERIE G NOITE ANUAL - 41753987</t>
   </si>
   <si>
-    <t>8º ANO D INTEGRAL 7H T1 ANUAL - 40907749</t>
+    <t>8º ANO E INTEGRAL 7H T1 ANUAL - 40907753</t>
+  </si>
+  <si>
+    <t>9° ANO A INTEGRAL 7H T1 ANUAL - 40907750</t>
   </si>
   <si>
     <t>4050 - ADMINISTRAÇÃO - 2ª SERIE A INTEGRAL 7H T2 ANUAL - 41139012</t>
   </si>
   <si>
-    <t>8º ANO E INTEGRAL 7H T1 ANUAL - 40907753</t>
+    <t>9° ANO B INTEGRAL 7H T1 ANUAL - 40907745</t>
+  </si>
+  <si>
+    <t>9° ANO C INTEGRAL 7H T1 ANUAL - 40907754</t>
   </si>
   <si>
     <t>4050 - ADMINISTRAÇÃO - 2ª SERIE B INTEGRAL 7H T2 ANUAL - 41139013</t>
   </si>
   <si>
-    <t>9° ANO A INTEGRAL 7H T1 ANUAL - 40907750</t>
-  </si>
-  <si>
-    <t>9° ANO B INTEGRAL 7H T1 ANUAL - 40907745</t>
-  </si>
-  <si>
     <t>6082 - DESENVOLVIMENTO DE SISTEMAS - 2ª SERIE C INTEGRAL 7H T2 ANUAL - 41234675</t>
-  </si>
-  <si>
-    <t>9° ANO C INTEGRAL 7H T1 ANUAL - 40907754</t>
   </si>
   <si>
     <t>-</t>
@@ -702,72 +702,100 @@
   <sheetData>
     <row r="1" ht="64.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4">
         <v>37.0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="C2" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>84.0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>43.0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>64.0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>36.0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>49.0</v>
+      </c>
       <c r="J2" s="4">
         <f t="shared" ref="J2:J17" si="1">IF(COUNT(D2:I2)&gt;0, SUM(D2:I2), 0)</f>
-        <v>0</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4">
         <v>36.0</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="C3" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>84.0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>57.0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>66.0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>38.0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>54.0</v>
+      </c>
       <c r="J3" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4">
@@ -777,111 +805,195 @@
       <c r="B4" s="4">
         <v>36.0</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="C4" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>74.0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>51.0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>57.0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>42.0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>48.0</v>
+      </c>
       <c r="J4" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="4">
         <v>38.0</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="C5" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>90.0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>55.0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>60.0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>48.0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>37.0</v>
+      </c>
       <c r="J5" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="4">
         <v>32.0</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="C6" s="5">
+        <v>26.0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>63.0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>45.0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>49.0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>49.0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>37.0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>49.0</v>
+      </c>
       <c r="J6" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>33.0</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="C7" s="5">
+        <v>29.0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>64.0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>42.0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>42.0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>46.0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>43.0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>41.0</v>
+      </c>
       <c r="J7" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>33.0</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="C8" s="5">
+        <v>29.0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>59.0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>41.0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>49.0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>49.0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>37.0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>49.0</v>
+      </c>
       <c r="J8" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="4">
         <v>35.0</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="C9" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>63.0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>43.0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>54.0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>54.0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>49.0</v>
+      </c>
       <c r="J9" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -891,16 +1003,30 @@
       <c r="B10" s="4">
         <v>35.0</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="C10" s="5">
+        <v>32.0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>94.0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>59.0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>59.0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>52.0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>45.0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>39.0</v>
+      </c>
       <c r="J10" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11">
@@ -910,16 +1036,30 @@
       <c r="B11" s="4">
         <v>35.0</v>
       </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="C11" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>65.0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>67.0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>53.0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>57.0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>54.0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>44.0</v>
+      </c>
       <c r="J11" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12">
@@ -929,111 +1069,195 @@
       <c r="B12" s="4">
         <v>30.0</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="C12" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>70.0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>43.0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>50.0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>54.0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>44.0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>21.0</v>
+      </c>
       <c r="J12" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="4">
         <v>32.0</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="C13" s="5">
+        <v>28.0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>59.0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>29.0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>41.0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>41.0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>35.0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>33.0</v>
+      </c>
       <c r="J13" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" s="4">
         <v>28.0</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="C14" s="5">
+        <v>25.0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>76.0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>48.0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>47.0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>44.0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>25.0</v>
+      </c>
       <c r="J14" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" s="4">
         <v>37.0</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="C15" s="5">
+        <v>33.0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>77.0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>39.0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>60.0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>57.0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>30.0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>38.0</v>
+      </c>
       <c r="J15" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="4">
         <v>35.0</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="C16" s="5">
+        <v>29.0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>64.0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>27.0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>38.0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>50.0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>22.0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>38.0</v>
+      </c>
       <c r="J16" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B17" s="4">
         <v>38.0</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="C17" s="5">
+        <v>31.0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>65.0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>37.0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>42.0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>51.0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>24.0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>32.0</v>
+      </c>
       <c r="J17" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2041,45 +2265,45 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B2" s="4">
         <v>32.0</v>
@@ -2121,7 +2345,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B3" s="4">
         <v>27.0</v>
@@ -2163,7 +2387,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>27.0</v>
@@ -2205,7 +2429,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B5" s="4">
         <v>28.0</v>
@@ -2245,7 +2469,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B6" s="4">
         <v>39.0</v>
@@ -2287,7 +2511,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4">
         <v>38.0</v>
@@ -2371,7 +2595,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="4">
         <v>29.0</v>
@@ -2413,7 +2637,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10" s="4">
         <v>22.0</v>
@@ -2455,7 +2679,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="4">
         <v>26.0</v>
@@ -2497,7 +2721,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" s="4">
         <v>18.0</v>
@@ -3539,36 +3763,36 @@
   <sheetData>
     <row r="1" ht="64.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4">
         <v>22.0</v>
@@ -3598,7 +3822,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4">
         <v>39.0</v>
@@ -3628,7 +3852,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" s="4">
         <v>40.0</v>
@@ -3658,7 +3882,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B5" s="4">
         <v>39.0</v>
@@ -3688,7 +3912,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B6" s="4">
         <v>39.0</v>
@@ -3718,7 +3942,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B7" s="4">
         <v>38.0</v>
@@ -3748,7 +3972,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B8" s="4">
         <v>16.0</v>
@@ -4778,52 +5002,52 @@
   <sheetData>
     <row r="1" ht="45.0" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1">
@@ -4832,7 +5056,7 @@
       </c>
       <c r="B2" s="7">
         <f t="shared" ref="B2:C2" si="1">IFERROR(SUM(B3:B36), 0)</f>
-        <v>400</v>
+        <v>872</v>
       </c>
       <c r="C2" s="7">
         <f t="shared" si="1"/>
@@ -4840,7 +5064,7 @@
       </c>
       <c r="D2" s="8">
         <f t="shared" ref="D2:D36" si="3">IF(AND(ISNUMBER(C2), C2&gt;0, ISNUMBER(B2)), B2/C2, 0)</f>
-        <v>0.3619909502</v>
+        <v>0.7891402715</v>
       </c>
       <c r="E2" s="8">
         <f t="shared" ref="E2:P2" si="2">IFERROR(AVERAGEIF(E3:E36, "&gt;0"), 0)</f>
@@ -4848,7 +5072,7 @@
       </c>
       <c r="F2" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5480963022</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" si="2"/>
@@ -4864,23 +5088,23 @@
       </c>
       <c r="J2" s="8">
         <f t="shared" si="2"/>
-        <v>0.4243164562</v>
+        <v>0.4429632675</v>
       </c>
       <c r="K2" s="8">
         <f t="shared" si="2"/>
-        <v>0.5967151436</v>
+        <v>0.507126923</v>
       </c>
       <c r="L2" s="8">
         <f t="shared" si="2"/>
-        <v>0.5885381682</v>
+        <v>0.5883681966</v>
       </c>
       <c r="M2" s="8">
         <f t="shared" si="2"/>
-        <v>0.606655385</v>
+        <v>0.6087044696</v>
       </c>
       <c r="N2" s="8">
         <f t="shared" si="2"/>
-        <v>0.445714945</v>
+        <v>0.4121505026</v>
       </c>
       <c r="O2" s="8">
         <f t="shared" si="2"/>
@@ -4888,16 +5112,16 @@
       </c>
       <c r="P2" s="8">
         <f t="shared" si="2"/>
-        <v>0.5063200406</v>
+        <v>0.5020758822</v>
       </c>
     </row>
     <row r="3" ht="21.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="10" t="str">
+        <v>42</v>
+      </c>
+      <c r="B3" s="10">
         <f>'6º ao 9º EFAF'!C2</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="C3" s="10">
         <f>'6º ao 9º EFAF'!B2</f>
@@ -4905,14 +5129,14 @@
       </c>
       <c r="D3" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8378378378</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F3" s="13">
         <f>IF(AND(ISNUMBER(B3), B3&gt;0, ISNUMBER('6º ao 9º EFAF'!G2)), ('6º ao 9º EFAF'!G2/(B3*3)), 0)</f>
-        <v>0</v>
+        <v>0.3870967742</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>75</v>
@@ -4925,39 +5149,39 @@
       </c>
       <c r="J3" s="13">
         <f>IF(AND(ISNUMBER(B3), B3&gt;0, ISNUMBER('6º ao 9º EFAF'!I2)), ('6º ao 9º EFAF'!I2/(B3*3)), 0)</f>
-        <v>0</v>
+        <v>0.5268817204</v>
       </c>
       <c r="K3" s="13">
         <f>IF(AND(ISNUMBER(B3), B3&gt;0, ISNUMBER('6º ao 9º EFAF'!H2)), ('6º ao 9º EFAF'!H2/(B3*3)), 0)</f>
-        <v>0</v>
+        <v>0.3010752688</v>
       </c>
       <c r="L3" s="13">
         <f>IF(AND(ISNUMBER(B3), B3&gt;0, ISNUMBER('6º ao 9º EFAF'!F2)), ('6º ao 9º EFAF'!F2/(B3*3)), 0)</f>
-        <v>0</v>
+        <v>0.688172043</v>
       </c>
       <c r="M3" s="13">
         <f>IF(AND(ISNUMBER(B3), B3&gt;0, ISNUMBER('6º ao 9º EFAF'!D2)), ('6º ao 9º EFAF'!D2/(B3*4)), 0)</f>
-        <v>0</v>
+        <v>0.6774193548</v>
       </c>
       <c r="N3" s="13">
         <f>IF(AND(ISNUMBER(B3), B3&gt;0, ISNUMBER('6º ao 9º EFAF'!E2)), ('6º ao 9º EFAF'!E2/(B3*4)), 0)</f>
-        <v>0</v>
+        <v>0.3467741935</v>
       </c>
       <c r="O3" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P3" s="14">
         <f t="shared" ref="P3:P36" si="4">IFERROR(AVERAGEIF(E3:O3, "&gt;0"), 0)</f>
-        <v>0</v>
+        <v>0.4879032258</v>
       </c>
     </row>
     <row r="4" ht="21.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="10" t="str">
+        <v>45</v>
+      </c>
+      <c r="B4" s="10">
         <f>'6º ao 9º EFAF'!C3</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="C4" s="10">
         <f>'6º ao 9º EFAF'!B3</f>
@@ -4965,14 +5189,14 @@
       </c>
       <c r="D4" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8611111111</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F4" s="13">
         <f>IF(AND(ISNUMBER(B4), B4&gt;0, ISNUMBER('6º ao 9º EFAF'!G3)), ('6º ao 9º EFAF'!G3/(B4*3)), 0)</f>
-        <v>0</v>
+        <v>0.4086021505</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>75</v>
@@ -4985,39 +5209,39 @@
       </c>
       <c r="J4" s="13">
         <f>IF(AND(ISNUMBER(B4), B4&gt;0, ISNUMBER('6º ao 9º EFAF'!I3)), ('6º ao 9º EFAF'!I3/(B4*3)), 0)</f>
-        <v>0</v>
+        <v>0.5806451613</v>
       </c>
       <c r="K4" s="13">
         <f>IF(AND(ISNUMBER(B4), B4&gt;0, ISNUMBER('6º ao 9º EFAF'!H3)), ('6º ao 9º EFAF'!H3/(B4*3)), 0)</f>
-        <v>0</v>
+        <v>0.3225806452</v>
       </c>
       <c r="L4" s="13">
         <f>IF(AND(ISNUMBER(B4), B4&gt;0, ISNUMBER('6º ao 9º EFAF'!F3)), ('6º ao 9º EFAF'!F3/(B4*3)), 0)</f>
-        <v>0</v>
+        <v>0.7096774194</v>
       </c>
       <c r="M4" s="13">
         <f>IF(AND(ISNUMBER(B4), B4&gt;0, ISNUMBER('6º ao 9º EFAF'!D3)), ('6º ao 9º EFAF'!D3/(B4*4)), 0)</f>
-        <v>0</v>
+        <v>0.6774193548</v>
       </c>
       <c r="N4" s="13">
         <f>IF(AND(ISNUMBER(B4), B4&gt;0, ISNUMBER('6º ao 9º EFAF'!E3)), ('6º ao 9º EFAF'!E3/(B4*4)), 0)</f>
-        <v>0</v>
+        <v>0.4596774194</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P4" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5264336918</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="10" t="str">
+      <c r="B5" s="10">
         <f>'6º ao 9º EFAF'!C4</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="C5" s="10">
         <f>'6º ao 9º EFAF'!B4</f>
@@ -5025,14 +5249,14 @@
       </c>
       <c r="D5" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.7777777778</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F5" s="13">
         <f>IF(AND(ISNUMBER(B5), B5&gt;0, ISNUMBER('6º ao 9º EFAF'!G4)), ('6º ao 9º EFAF'!G4/(B5*3)), 0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>75</v>
@@ -5045,39 +5269,39 @@
       </c>
       <c r="J5" s="13">
         <f>IF(AND(ISNUMBER(B5), B5&gt;0, ISNUMBER('6º ao 9º EFAF'!I4)), ('6º ao 9º EFAF'!I4/(B5*3)), 0)</f>
-        <v>0</v>
+        <v>0.5714285714</v>
       </c>
       <c r="K5" s="13">
         <f>IF(AND(ISNUMBER(B5), B5&gt;0, ISNUMBER('6º ao 9º EFAF'!H4)), ('6º ao 9º EFAF'!H4/(B5*3)), 0)</f>
-        <v>0</v>
+        <v>0.3928571429</v>
       </c>
       <c r="L5" s="13">
         <f>IF(AND(ISNUMBER(B5), B5&gt;0, ISNUMBER('6º ao 9º EFAF'!F4)), ('6º ao 9º EFAF'!F4/(B5*3)), 0)</f>
-        <v>0</v>
+        <v>0.6785714286</v>
       </c>
       <c r="M5" s="13">
         <f>IF(AND(ISNUMBER(B5), B5&gt;0, ISNUMBER('6º ao 9º EFAF'!D4)), ('6º ao 9º EFAF'!D4/(B5*4)), 0)</f>
-        <v>0</v>
+        <v>0.6607142857</v>
       </c>
       <c r="N5" s="13">
         <f>IF(AND(ISNUMBER(B5), B5&gt;0, ISNUMBER('6º ao 9º EFAF'!E4)), ('6º ao 9º EFAF'!E4/(B5*4)), 0)</f>
-        <v>0</v>
+        <v>0.4553571429</v>
       </c>
       <c r="O5" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5431547619</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="10" t="str">
+        <v>50</v>
+      </c>
+      <c r="B6" s="10">
         <f>'6º ao 9º EFAF'!C5</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="C6" s="10">
         <f>'6º ao 9º EFAF'!B5</f>
@@ -5085,14 +5309,14 @@
       </c>
       <c r="D6" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8684210526</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F6" s="13">
         <f>IF(AND(ISNUMBER(B6), B6&gt;0, ISNUMBER('6º ao 9º EFAF'!G5)), ('6º ao 9º EFAF'!G5/(B6*3)), 0)</f>
-        <v>0</v>
+        <v>0.4848484848</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>75</v>
@@ -5105,39 +5329,39 @@
       </c>
       <c r="J6" s="13">
         <f>IF(AND(ISNUMBER(B6), B6&gt;0, ISNUMBER('6º ao 9º EFAF'!I5)), ('6º ao 9º EFAF'!I5/(B6*3)), 0)</f>
-        <v>0</v>
+        <v>0.3737373737</v>
       </c>
       <c r="K6" s="13">
         <f>IF(AND(ISNUMBER(B6), B6&gt;0, ISNUMBER('6º ao 9º EFAF'!H5)), ('6º ao 9º EFAF'!H5/(B6*3)), 0)</f>
-        <v>0</v>
+        <v>0.2828282828</v>
       </c>
       <c r="L6" s="13">
         <f>IF(AND(ISNUMBER(B6), B6&gt;0, ISNUMBER('6º ao 9º EFAF'!F5)), ('6º ao 9º EFAF'!F5/(B6*3)), 0)</f>
-        <v>0</v>
+        <v>0.6060606061</v>
       </c>
       <c r="M6" s="13">
         <f>IF(AND(ISNUMBER(B6), B6&gt;0, ISNUMBER('6º ao 9º EFAF'!D5)), ('6º ao 9º EFAF'!D5/(B6*4)), 0)</f>
-        <v>0</v>
+        <v>0.6818181818</v>
       </c>
       <c r="N6" s="13">
         <f>IF(AND(ISNUMBER(B6), B6&gt;0, ISNUMBER('6º ao 9º EFAF'!E5)), ('6º ao 9º EFAF'!E5/(B6*4)), 0)</f>
-        <v>0</v>
+        <v>0.4166666667</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4743265993</v>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="10" t="str">
+        <v>52</v>
+      </c>
+      <c r="B7" s="10">
         <f>'6º ao 9º EFAF'!C6</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="C7" s="10">
         <f>'6º ao 9º EFAF'!B6</f>
@@ -5145,14 +5369,14 @@
       </c>
       <c r="D7" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8125</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F7" s="13">
         <f>IF(AND(ISNUMBER(B7), B7&gt;0, ISNUMBER('6º ao 9º EFAF'!G6)), ('6º ao 9º EFAF'!G6/(B7*3)), 0)</f>
-        <v>0</v>
+        <v>0.6282051282</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>75</v>
@@ -5165,39 +5389,39 @@
       </c>
       <c r="J7" s="13">
         <f>IF(AND(ISNUMBER(B7), B7&gt;0, ISNUMBER('6º ao 9º EFAF'!I6)), ('6º ao 9º EFAF'!I6/(B7*3)), 0)</f>
-        <v>0</v>
+        <v>0.6282051282</v>
       </c>
       <c r="K7" s="13">
         <f>IF(AND(ISNUMBER(B7), B7&gt;0, ISNUMBER('6º ao 9º EFAF'!H6)), ('6º ao 9º EFAF'!H6/(B7*3)), 0)</f>
-        <v>0</v>
+        <v>0.4743589744</v>
       </c>
       <c r="L7" s="13">
         <f>IF(AND(ISNUMBER(B7), B7&gt;0, ISNUMBER('6º ao 9º EFAF'!F6)), ('6º ao 9º EFAF'!F6/(B7*3)), 0)</f>
-        <v>0</v>
+        <v>0.6282051282</v>
       </c>
       <c r="M7" s="13">
         <f>IF(AND(ISNUMBER(B7), B7&gt;0, ISNUMBER('6º ao 9º EFAF'!D6)), ('6º ao 9º EFAF'!D6/(B7*4)), 0)</f>
-        <v>0</v>
+        <v>0.6057692308</v>
       </c>
       <c r="N7" s="13">
         <f>IF(AND(ISNUMBER(B7), B7&gt;0, ISNUMBER('6º ao 9º EFAF'!E6)), ('6º ao 9º EFAF'!E6/(B7*4)), 0)</f>
-        <v>0</v>
+        <v>0.4326923077</v>
       </c>
       <c r="O7" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5662393162</v>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="10" t="str">
+        <v>57</v>
+      </c>
+      <c r="B8" s="10">
         <f>'6º ao 9º EFAF'!C7</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="C8" s="10">
         <f>'6º ao 9º EFAF'!B7</f>
@@ -5205,14 +5429,14 @@
       </c>
       <c r="D8" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8787878788</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F8" s="13">
         <f>IF(AND(ISNUMBER(B8), B8&gt;0, ISNUMBER('6º ao 9º EFAF'!G7)), ('6º ao 9º EFAF'!G7/(B8*3)), 0)</f>
-        <v>0</v>
+        <v>0.5287356322</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>75</v>
@@ -5225,39 +5449,39 @@
       </c>
       <c r="J8" s="13">
         <f>IF(AND(ISNUMBER(B8), B8&gt;0, ISNUMBER('6º ao 9º EFAF'!I7)), ('6º ao 9º EFAF'!I7/(B8*3)), 0)</f>
-        <v>0</v>
+        <v>0.4712643678</v>
       </c>
       <c r="K8" s="13">
         <f>IF(AND(ISNUMBER(B8), B8&gt;0, ISNUMBER('6º ao 9º EFAF'!H7)), ('6º ao 9º EFAF'!H7/(B8*3)), 0)</f>
-        <v>0</v>
+        <v>0.4942528736</v>
       </c>
       <c r="L8" s="13">
         <f>IF(AND(ISNUMBER(B8), B8&gt;0, ISNUMBER('6º ao 9º EFAF'!F7)), ('6º ao 9º EFAF'!F7/(B8*3)), 0)</f>
-        <v>0</v>
+        <v>0.4827586207</v>
       </c>
       <c r="M8" s="13">
         <f>IF(AND(ISNUMBER(B8), B8&gt;0, ISNUMBER('6º ao 9º EFAF'!D7)), ('6º ao 9º EFAF'!D7/(B8*4)), 0)</f>
-        <v>0</v>
+        <v>0.5517241379</v>
       </c>
       <c r="N8" s="13">
         <f>IF(AND(ISNUMBER(B8), B8&gt;0, ISNUMBER('6º ao 9º EFAF'!E7)), ('6º ao 9º EFAF'!E7/(B8*4)), 0)</f>
-        <v>0</v>
+        <v>0.3620689655</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4818007663</v>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="10" t="str">
+        <v>58</v>
+      </c>
+      <c r="B9" s="10">
         <f>'6º ao 9º EFAF'!C8</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="C9" s="10">
         <f>'6º ao 9º EFAF'!B8</f>
@@ -5265,14 +5489,14 @@
       </c>
       <c r="D9" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8787878788</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F9" s="13">
         <f>IF(AND(ISNUMBER(B9), B9&gt;0, ISNUMBER('6º ao 9º EFAF'!G8)), ('6º ao 9º EFAF'!G8/(B9*3)), 0)</f>
-        <v>0</v>
+        <v>0.5632183908</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>75</v>
@@ -5285,39 +5509,39 @@
       </c>
       <c r="J9" s="13">
         <f>IF(AND(ISNUMBER(B9), B9&gt;0, ISNUMBER('6º ao 9º EFAF'!I8)), ('6º ao 9º EFAF'!I8/(B9*3)), 0)</f>
-        <v>0</v>
+        <v>0.5632183908</v>
       </c>
       <c r="K9" s="13">
         <f>IF(AND(ISNUMBER(B9), B9&gt;0, ISNUMBER('6º ao 9º EFAF'!H8)), ('6º ao 9º EFAF'!H8/(B9*3)), 0)</f>
-        <v>0</v>
+        <v>0.4252873563</v>
       </c>
       <c r="L9" s="13">
         <f>IF(AND(ISNUMBER(B9), B9&gt;0, ISNUMBER('6º ao 9º EFAF'!F8)), ('6º ao 9º EFAF'!F8/(B9*3)), 0)</f>
-        <v>0</v>
+        <v>0.5632183908</v>
       </c>
       <c r="M9" s="13">
         <f>IF(AND(ISNUMBER(B9), B9&gt;0, ISNUMBER('6º ao 9º EFAF'!D8)), ('6º ao 9º EFAF'!D8/(B9*4)), 0)</f>
-        <v>0</v>
+        <v>0.5086206897</v>
       </c>
       <c r="N9" s="13">
         <f>IF(AND(ISNUMBER(B9), B9&gt;0, ISNUMBER('6º ao 9º EFAF'!E8)), ('6º ao 9º EFAF'!E8/(B9*4)), 0)</f>
-        <v>0</v>
+        <v>0.3534482759</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P9" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4961685824</v>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="10" t="str">
+        <v>60</v>
+      </c>
+      <c r="B10" s="10">
         <f>'6º ao 9º EFAF'!C9</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="C10" s="10">
         <f>'6º ao 9º EFAF'!B9</f>
@@ -5325,14 +5549,14 @@
       </c>
       <c r="D10" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8857142857</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F10" s="13">
         <f>IF(AND(ISNUMBER(B10), B10&gt;0, ISNUMBER('6º ao 9º EFAF'!G9)), ('6º ao 9º EFAF'!G9/(B10*3)), 0)</f>
-        <v>0</v>
+        <v>0.5806451613</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>75</v>
@@ -5345,39 +5569,39 @@
       </c>
       <c r="J10" s="13">
         <f>IF(AND(ISNUMBER(B10), B10&gt;0, ISNUMBER('6º ao 9º EFAF'!I9)), ('6º ao 9º EFAF'!I9/(B10*3)), 0)</f>
-        <v>0</v>
+        <v>0.5268817204</v>
       </c>
       <c r="K10" s="13">
         <f>IF(AND(ISNUMBER(B10), B10&gt;0, ISNUMBER('6º ao 9º EFAF'!H9)), ('6º ao 9º EFAF'!H9/(B10*3)), 0)</f>
-        <v>0</v>
+        <v>0.3548387097</v>
       </c>
       <c r="L10" s="13">
         <f>IF(AND(ISNUMBER(B10), B10&gt;0, ISNUMBER('6º ao 9º EFAF'!F9)), ('6º ao 9º EFAF'!F9/(B10*3)), 0)</f>
-        <v>0</v>
+        <v>0.5806451613</v>
       </c>
       <c r="M10" s="13">
         <f>IF(AND(ISNUMBER(B10), B10&gt;0, ISNUMBER('6º ao 9º EFAF'!D9)), ('6º ao 9º EFAF'!D9/(B10*4)), 0)</f>
-        <v>0</v>
+        <v>0.5080645161</v>
       </c>
       <c r="N10" s="13">
         <f>IF(AND(ISNUMBER(B10), B10&gt;0, ISNUMBER('6º ao 9º EFAF'!E9)), ('6º ao 9º EFAF'!E9/(B10*4)), 0)</f>
-        <v>0</v>
+        <v>0.3467741935</v>
       </c>
       <c r="O10" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4829749104</v>
       </c>
     </row>
     <row r="11" ht="21.75" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="10" t="str">
+      <c r="B11" s="10">
         <f>'6º ao 9º EFAF'!C10</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="C11" s="10">
         <f>'6º ao 9º EFAF'!B10</f>
@@ -5385,14 +5609,14 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.9142857143</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F11" s="13">
         <f>IF(AND(ISNUMBER(B11), B11&gt;0, ISNUMBER('6º ao 9º EFAF'!G10)), ('6º ao 9º EFAF'!G10/(B11*3)), 0)</f>
-        <v>0</v>
+        <v>0.5416666667</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>75</v>
@@ -5405,39 +5629,39 @@
       </c>
       <c r="J11" s="13">
         <f>IF(AND(ISNUMBER(B11), B11&gt;0, ISNUMBER('6º ao 9º EFAF'!I10)), ('6º ao 9º EFAF'!I10/(B11*3)), 0)</f>
-        <v>0</v>
+        <v>0.40625</v>
       </c>
       <c r="K11" s="13">
         <f>IF(AND(ISNUMBER(B11), B11&gt;0, ISNUMBER('6º ao 9º EFAF'!H10)), ('6º ao 9º EFAF'!H10/(B11*3)), 0)</f>
-        <v>0</v>
+        <v>0.46875</v>
       </c>
       <c r="L11" s="13">
         <f>IF(AND(ISNUMBER(B11), B11&gt;0, ISNUMBER('6º ao 9º EFAF'!F10)), ('6º ao 9º EFAF'!F10/(B11*3)), 0)</f>
-        <v>0</v>
+        <v>0.6145833333</v>
       </c>
       <c r="M11" s="13">
         <f>IF(AND(ISNUMBER(B11), B11&gt;0, ISNUMBER('6º ao 9º EFAF'!D10)), ('6º ao 9º EFAF'!D10/(B11*4)), 0)</f>
-        <v>0</v>
+        <v>0.734375</v>
       </c>
       <c r="N11" s="13">
         <f>IF(AND(ISNUMBER(B11), B11&gt;0, ISNUMBER('6º ao 9º EFAF'!E10)), ('6º ao 9º EFAF'!E10/(B11*4)), 0)</f>
-        <v>0</v>
+        <v>0.4609375</v>
       </c>
       <c r="O11" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5377604167</v>
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="10" t="str">
+      <c r="B12" s="10">
         <f>'6º ao 9º EFAF'!C11</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="C12" s="10">
         <f>'6º ao 9º EFAF'!B11</f>
@@ -5445,14 +5669,14 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8857142857</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F12" s="13">
         <f>IF(AND(ISNUMBER(B12), B12&gt;0, ISNUMBER('6º ao 9º EFAF'!G11)), ('6º ao 9º EFAF'!G11/(B12*3)), 0)</f>
-        <v>0</v>
+        <v>0.6129032258</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>75</v>
@@ -5465,39 +5689,39 @@
       </c>
       <c r="J12" s="13">
         <f>IF(AND(ISNUMBER(B12), B12&gt;0, ISNUMBER('6º ao 9º EFAF'!I11)), ('6º ao 9º EFAF'!I11/(B12*3)), 0)</f>
-        <v>0</v>
+        <v>0.4731182796</v>
       </c>
       <c r="K12" s="13">
         <f>IF(AND(ISNUMBER(B12), B12&gt;0, ISNUMBER('6º ao 9º EFAF'!H11)), ('6º ao 9º EFAF'!H11/(B12*3)), 0)</f>
-        <v>0</v>
+        <v>0.5806451613</v>
       </c>
       <c r="L12" s="13">
         <f>IF(AND(ISNUMBER(B12), B12&gt;0, ISNUMBER('6º ao 9º EFAF'!F11)), ('6º ao 9º EFAF'!F11/(B12*3)), 0)</f>
-        <v>0</v>
+        <v>0.5698924731</v>
       </c>
       <c r="M12" s="13">
         <f>IF(AND(ISNUMBER(B12), B12&gt;0, ISNUMBER('6º ao 9º EFAF'!D11)), ('6º ao 9º EFAF'!D11/(B12*4)), 0)</f>
-        <v>0</v>
+        <v>0.5241935484</v>
       </c>
       <c r="N12" s="13">
         <f>IF(AND(ISNUMBER(B12), B12&gt;0, ISNUMBER('6º ao 9º EFAF'!E11)), ('6º ao 9º EFAF'!E11/(B12*4)), 0)</f>
-        <v>0</v>
+        <v>0.5403225806</v>
       </c>
       <c r="O12" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5501792115</v>
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="10" t="str">
+      <c r="B13" s="10">
         <f>'6º ao 9º EFAF'!C12</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="C13" s="10">
         <f>'6º ao 9º EFAF'!B12</f>
@@ -5505,14 +5729,14 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8333333333</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F13" s="13">
         <f>IF(AND(ISNUMBER(B13), B13&gt;0, ISNUMBER('6º ao 9º EFAF'!G12)), ('6º ao 9º EFAF'!G12/(B13*3)), 0)</f>
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>75</v>
@@ -5525,39 +5749,39 @@
       </c>
       <c r="J13" s="13">
         <f>IF(AND(ISNUMBER(B13), B13&gt;0, ISNUMBER('6º ao 9º EFAF'!I12)), ('6º ao 9º EFAF'!I12/(B13*3)), 0)</f>
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="K13" s="13">
         <f>IF(AND(ISNUMBER(B13), B13&gt;0, ISNUMBER('6º ao 9º EFAF'!H12)), ('6º ao 9º EFAF'!H12/(B13*3)), 0)</f>
-        <v>0</v>
+        <v>0.5866666667</v>
       </c>
       <c r="L13" s="13">
         <f>IF(AND(ISNUMBER(B13), B13&gt;0, ISNUMBER('6º ao 9º EFAF'!F12)), ('6º ao 9º EFAF'!F12/(B13*3)), 0)</f>
-        <v>0</v>
+        <v>0.6666666667</v>
       </c>
       <c r="M13" s="13">
         <f>IF(AND(ISNUMBER(B13), B13&gt;0, ISNUMBER('6º ao 9º EFAF'!D12)), ('6º ao 9º EFAF'!D12/(B13*4)), 0)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N13" s="13">
         <f>IF(AND(ISNUMBER(B13), B13&gt;0, ISNUMBER('6º ao 9º EFAF'!E12)), ('6º ao 9º EFAF'!E12/(B13*4)), 0)</f>
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="O13" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P13" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5638888889</v>
       </c>
     </row>
     <row r="14" ht="21.75" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="10" t="str">
+        <v>66</v>
+      </c>
+      <c r="B14" s="10">
         <f>'6º ao 9º EFAF'!C13</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="C14" s="10">
         <f>'6º ao 9º EFAF'!B13</f>
@@ -5565,14 +5789,14 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F14" s="13">
         <f>IF(AND(ISNUMBER(B14), B14&gt;0, ISNUMBER('6º ao 9º EFAF'!G13)), ('6º ao 9º EFAF'!G13/(B14*3)), 0)</f>
-        <v>0</v>
+        <v>0.4880952381</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>75</v>
@@ -5585,39 +5809,39 @@
       </c>
       <c r="J14" s="13">
         <f>IF(AND(ISNUMBER(B14), B14&gt;0, ISNUMBER('6º ao 9º EFAF'!I13)), ('6º ao 9º EFAF'!I13/(B14*3)), 0)</f>
-        <v>0</v>
+        <v>0.3928571429</v>
       </c>
       <c r="K14" s="13">
         <f>IF(AND(ISNUMBER(B14), B14&gt;0, ISNUMBER('6º ao 9º EFAF'!H13)), ('6º ao 9º EFAF'!H13/(B14*3)), 0)</f>
-        <v>0</v>
+        <v>0.4166666667</v>
       </c>
       <c r="L14" s="13">
         <f>IF(AND(ISNUMBER(B14), B14&gt;0, ISNUMBER('6º ao 9º EFAF'!F13)), ('6º ao 9º EFAF'!F13/(B14*3)), 0)</f>
-        <v>0</v>
+        <v>0.4880952381</v>
       </c>
       <c r="M14" s="13">
         <f>IF(AND(ISNUMBER(B14), B14&gt;0, ISNUMBER('6º ao 9º EFAF'!D13)), ('6º ao 9º EFAF'!D13/(B14*4)), 0)</f>
-        <v>0</v>
+        <v>0.5267857143</v>
       </c>
       <c r="N14" s="13">
         <f>IF(AND(ISNUMBER(B14), B14&gt;0, ISNUMBER('6º ao 9º EFAF'!E13)), ('6º ao 9º EFAF'!E13/(B14*4)), 0)</f>
-        <v>0</v>
+        <v>0.2589285714</v>
       </c>
       <c r="O14" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P14" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4285714286</v>
       </c>
     </row>
     <row r="15" ht="21.75" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="10" t="str">
+        <v>68</v>
+      </c>
+      <c r="B15" s="10">
         <f>'6º ao 9º EFAF'!C14</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="C15" s="10">
         <f>'6º ao 9º EFAF'!B14</f>
@@ -5625,14 +5849,14 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8928571429</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F15" s="13">
         <f>IF(AND(ISNUMBER(B15), B15&gt;0, ISNUMBER('6º ao 9º EFAF'!G14)), ('6º ao 9º EFAF'!G14/(B15*3)), 0)</f>
-        <v>0</v>
+        <v>0.6266666667</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>75</v>
@@ -5645,39 +5869,39 @@
       </c>
       <c r="J15" s="13">
         <f>IF(AND(ISNUMBER(B15), B15&gt;0, ISNUMBER('6º ao 9º EFAF'!I14)), ('6º ao 9º EFAF'!I14/(B15*3)), 0)</f>
-        <v>0</v>
+        <v>0.3333333333</v>
       </c>
       <c r="K15" s="13">
         <f>IF(AND(ISNUMBER(B15), B15&gt;0, ISNUMBER('6º ao 9º EFAF'!H14)), ('6º ao 9º EFAF'!H14/(B15*3)), 0)</f>
-        <v>0</v>
+        <v>0.5866666667</v>
       </c>
       <c r="L15" s="13">
         <f>IF(AND(ISNUMBER(B15), B15&gt;0, ISNUMBER('6º ao 9º EFAF'!F14)), ('6º ao 9º EFAF'!F14/(B15*3)), 0)</f>
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="M15" s="13">
         <f>IF(AND(ISNUMBER(B15), B15&gt;0, ISNUMBER('6º ao 9º EFAF'!D14)), ('6º ao 9º EFAF'!D14/(B15*4)), 0)</f>
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="N15" s="13">
         <f>IF(AND(ISNUMBER(B15), B15&gt;0, ISNUMBER('6º ao 9º EFAF'!E14)), ('6º ao 9º EFAF'!E14/(B15*4)), 0)</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O15" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P15" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.5411111111</v>
       </c>
     </row>
     <row r="16" ht="21.75" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="10" t="str">
+        <v>69</v>
+      </c>
+      <c r="B16" s="10">
         <f>'6º ao 9º EFAF'!C15</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="C16" s="10">
         <f>'6º ao 9º EFAF'!B15</f>
@@ -5685,14 +5909,14 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8918918919</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F16" s="13">
         <f>IF(AND(ISNUMBER(B16), B16&gt;0, ISNUMBER('6º ao 9º EFAF'!G15)), ('6º ao 9º EFAF'!G15/(B16*3)), 0)</f>
-        <v>0</v>
+        <v>0.5757575758</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>75</v>
@@ -5705,39 +5929,39 @@
       </c>
       <c r="J16" s="13">
         <f>IF(AND(ISNUMBER(B16), B16&gt;0, ISNUMBER('6º ao 9º EFAF'!I15)), ('6º ao 9º EFAF'!I15/(B16*3)), 0)</f>
-        <v>0</v>
+        <v>0.3838383838</v>
       </c>
       <c r="K16" s="13">
         <f>IF(AND(ISNUMBER(B16), B16&gt;0, ISNUMBER('6º ao 9º EFAF'!H15)), ('6º ao 9º EFAF'!H15/(B16*3)), 0)</f>
-        <v>0</v>
+        <v>0.303030303</v>
       </c>
       <c r="L16" s="13">
         <f>IF(AND(ISNUMBER(B16), B16&gt;0, ISNUMBER('6º ao 9º EFAF'!F15)), ('6º ao 9º EFAF'!F15/(B16*3)), 0)</f>
-        <v>0</v>
+        <v>0.6060606061</v>
       </c>
       <c r="M16" s="13">
         <f>IF(AND(ISNUMBER(B16), B16&gt;0, ISNUMBER('6º ao 9º EFAF'!D15)), ('6º ao 9º EFAF'!D15/(B16*4)), 0)</f>
-        <v>0</v>
+        <v>0.5833333333</v>
       </c>
       <c r="N16" s="13">
         <f>IF(AND(ISNUMBER(B16), B16&gt;0, ISNUMBER('6º ao 9º EFAF'!E15)), ('6º ao 9º EFAF'!E15/(B16*4)), 0)</f>
-        <v>0</v>
+        <v>0.2954545455</v>
       </c>
       <c r="O16" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P16" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4579124579</v>
       </c>
     </row>
     <row r="17" ht="21.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="10" t="str">
+        <v>71</v>
+      </c>
+      <c r="B17" s="10">
         <f>'6º ao 9º EFAF'!C16</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="C17" s="10">
         <f>'6º ao 9º EFAF'!B16</f>
@@ -5745,14 +5969,14 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8285714286</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F17" s="13">
         <f>IF(AND(ISNUMBER(B17), B17&gt;0, ISNUMBER('6º ao 9º EFAF'!G16)), ('6º ao 9º EFAF'!G16/(B17*3)), 0)</f>
-        <v>0</v>
+        <v>0.5747126437</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>75</v>
@@ -5765,39 +5989,39 @@
       </c>
       <c r="J17" s="13">
         <f>IF(AND(ISNUMBER(B17), B17&gt;0, ISNUMBER('6º ao 9º EFAF'!I16)), ('6º ao 9º EFAF'!I16/(B17*3)), 0)</f>
-        <v>0</v>
+        <v>0.4367816092</v>
       </c>
       <c r="K17" s="13">
         <f>IF(AND(ISNUMBER(B17), B17&gt;0, ISNUMBER('6º ao 9º EFAF'!H16)), ('6º ao 9º EFAF'!H16/(B17*3)), 0)</f>
-        <v>0</v>
+        <v>0.2528735632</v>
       </c>
       <c r="L17" s="13">
         <f>IF(AND(ISNUMBER(B17), B17&gt;0, ISNUMBER('6º ao 9º EFAF'!F16)), ('6º ao 9º EFAF'!F16/(B17*3)), 0)</f>
-        <v>0</v>
+        <v>0.4367816092</v>
       </c>
       <c r="M17" s="13">
         <f>IF(AND(ISNUMBER(B17), B17&gt;0, ISNUMBER('6º ao 9º EFAF'!D16)), ('6º ao 9º EFAF'!D16/(B17*4)), 0)</f>
-        <v>0</v>
+        <v>0.5517241379</v>
       </c>
       <c r="N17" s="13">
         <f>IF(AND(ISNUMBER(B17), B17&gt;0, ISNUMBER('6º ao 9º EFAF'!E16)), ('6º ao 9º EFAF'!E16/(B17*4)), 0)</f>
-        <v>0</v>
+        <v>0.2327586207</v>
       </c>
       <c r="O17" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P17" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4142720307</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="10" t="str">
+        <v>72</v>
+      </c>
+      <c r="B18" s="10">
         <f>'6º ao 9º EFAF'!C17</f>
-        <v/>
+        <v>31</v>
       </c>
       <c r="C18" s="10">
         <f>'6º ao 9º EFAF'!B17</f>
@@ -5805,14 +6029,14 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8157894737</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>75</v>
       </c>
       <c r="F18" s="13">
         <f>IF(AND(ISNUMBER(B18), B18&gt;0, ISNUMBER('6º ao 9º EFAF'!G17)), ('6º ao 9º EFAF'!G17/(B18*3)), 0)</f>
-        <v>0</v>
+        <v>0.5483870968</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>75</v>
@@ -5825,35 +6049,35 @@
       </c>
       <c r="J18" s="13">
         <f>IF(AND(ISNUMBER(B18), B18&gt;0, ISNUMBER('6º ao 9º EFAF'!I17)), ('6º ao 9º EFAF'!I17/(B18*3)), 0)</f>
-        <v>0</v>
+        <v>0.3440860215</v>
       </c>
       <c r="K18" s="13">
         <f>IF(AND(ISNUMBER(B18), B18&gt;0, ISNUMBER('6º ao 9º EFAF'!H17)), ('6º ao 9º EFAF'!H17/(B18*3)), 0)</f>
-        <v>0</v>
+        <v>0.2580645161</v>
       </c>
       <c r="L18" s="13">
         <f>IF(AND(ISNUMBER(B18), B18&gt;0, ISNUMBER('6º ao 9º EFAF'!F17)), ('6º ao 9º EFAF'!F17/(B18*3)), 0)</f>
-        <v>0</v>
+        <v>0.4516129032</v>
       </c>
       <c r="M18" s="13">
         <f>IF(AND(ISNUMBER(B18), B18&gt;0, ISNUMBER('6º ao 9º EFAF'!D17)), ('6º ao 9º EFAF'!D17/(B18*4)), 0)</f>
-        <v>0</v>
+        <v>0.5241935484</v>
       </c>
       <c r="N18" s="13">
         <f>IF(AND(ISNUMBER(B18), B18&gt;0, ISNUMBER('6º ao 9º EFAF'!E17)), ('6º ao 9º EFAF'!E17/(B18*4)), 0)</f>
-        <v>0</v>
+        <v>0.2983870968</v>
       </c>
       <c r="O18" s="12" t="s">
         <v>75</v>
       </c>
       <c r="P18" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4041218638</v>
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B19" s="10">
         <f>'1ª e 2ª EM'!C2</f>
@@ -5916,7 +6140,7 @@
     </row>
     <row r="20" ht="21.75" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B20" s="10">
         <f>'1ª e 2ª EM'!C3</f>
@@ -5979,7 +6203,7 @@
     </row>
     <row r="21" ht="21.75" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B21" s="10">
         <f>'1ª e 2ª EM'!C4</f>
@@ -6042,7 +6266,7 @@
     </row>
     <row r="22" ht="21.75" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B22" s="10">
         <f>'1ª e 2ª EM'!C5</f>
@@ -6105,7 +6329,7 @@
     </row>
     <row r="23" ht="21.75" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B23" s="10">
         <f>'1ª e 2ª EM'!C6</f>
@@ -6168,7 +6392,7 @@
     </row>
     <row r="24" ht="21.75" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B24" s="10">
         <f>'1ª e 2ª EM'!C7</f>
@@ -6294,7 +6518,7 @@
     </row>
     <row r="26" ht="21.75" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="10">
         <f>'1ª e 2ª EM'!C9</f>
@@ -6357,7 +6581,7 @@
     </row>
     <row r="27" ht="21.75" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B27" s="10">
         <f>'1ª e 2ª EM'!C10</f>
@@ -6420,7 +6644,7 @@
     </row>
     <row r="28" ht="21.75" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B28" s="10">
         <f>'1ª e 2ª EM'!C11</f>
@@ -6483,7 +6707,7 @@
     </row>
     <row r="29" ht="21.75" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" s="10">
         <f>'1ª e 2ª EM'!C12</f>
@@ -6546,7 +6770,7 @@
     </row>
     <row r="30" ht="21.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B30" s="10">
         <f>'3ª EM'!C2</f>
@@ -6605,7 +6829,7 @@
     </row>
     <row r="31" ht="21.75" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B31" s="10">
         <f>'3ª EM'!C3</f>
@@ -6664,7 +6888,7 @@
     </row>
     <row r="32" ht="21.75" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B32" s="10">
         <f>'3ª EM'!C4</f>
@@ -6723,7 +6947,7 @@
     </row>
     <row r="33" ht="21.75" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B33" s="10">
         <f>'3ª EM'!C5</f>
@@ -6782,7 +7006,7 @@
     </row>
     <row r="34" ht="21.75" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B34" s="10">
         <f>'3ª EM'!C6</f>
@@ -6841,7 +7065,7 @@
     </row>
     <row r="35" ht="21.75" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B35" s="10">
         <f>'3ª EM'!C7</f>
@@ -6900,7 +7124,7 @@
     </row>
     <row r="36" ht="21.75" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B36" s="10">
         <f>'3ª EM'!C8</f>
